--- a/projects/fetch-ibkr-positions-dashboard.xlsx
+++ b/projects/fetch-ibkr-positions-dashboard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hongkiatkoh/Developer/timeless-workspace/projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35C69D2-CA22-0843-BFF6-B6E4BE9485E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F508FE0-DF8D-2842-9F94-DB9BB154C2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4120" yWindow="3000" windowWidth="38000" windowHeight="22840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20160" yWindow="600" windowWidth="31040" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -277,7 +277,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="206">
   <si>
     <t>HK</t>
   </si>
@@ -348,15 +348,9 @@
     <t>CSNDX</t>
   </si>
   <si>
-    <t>HEAL</t>
-  </si>
-  <si>
     <t>INRA</t>
   </si>
   <si>
-    <t>LOCK</t>
-  </si>
-  <si>
     <t>Best For</t>
   </si>
   <si>
@@ -642,9 +636,6 @@
     <t>ES3 (singapore banks)</t>
   </si>
   <si>
-    <t>VWRA (VT USD)</t>
-  </si>
-  <si>
     <t>Actual</t>
   </si>
   <si>
@@ -663,24 +654,15 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>WORLD (VT, no EM, hedged)</t>
-  </si>
-  <si>
     <t>CHF</t>
   </si>
   <si>
-    <t>Nasdaq (EQCH, hedged)</t>
-  </si>
-  <si>
     <t>Global Triads (the strategic core)</t>
   </si>
   <si>
     <t>Four Horsemen (growth engine)</t>
   </si>
   <si>
-    <t>The Vault (Gold)</t>
-  </si>
-  <si>
     <t>The War Chest (Cash)</t>
   </si>
   <si>
@@ -774,9 +756,6 @@
     <t>UK</t>
   </si>
   <si>
-    <t>1.1b</t>
-  </si>
-  <si>
     <t>2.1b</t>
   </si>
   <si>
@@ -792,18 +771,12 @@
     <t>1.0b</t>
   </si>
   <si>
-    <t>1.6b</t>
-  </si>
-  <si>
     <t>CurrencyPrimary</t>
   </si>
   <si>
     <t>Total Value USD</t>
   </si>
   <si>
-    <t>CNH</t>
-  </si>
-  <si>
     <t>The Omega (insurance, SPY and QQQ bear spreads)</t>
   </si>
   <si>
@@ -846,18 +819,12 @@
     <t>MSCI World Index, CHF-hedged, Large &amp; Mid-Cap stocks 23 developed countries</t>
   </si>
   <si>
-    <t xml:space="preserve">China Tech (CBUK, unhedged) </t>
-  </si>
-  <si>
     <t>Actual % of Total</t>
   </si>
   <si>
     <t>Cash vs Invested</t>
   </si>
   <si>
-    <t>Portfolio Allocation</t>
-  </si>
-  <si>
     <t>Core</t>
   </si>
   <si>
@@ -885,9 +852,6 @@
     <t>SMH</t>
   </si>
   <si>
-    <t>Nasdaq (CSNDX)</t>
-  </si>
-  <si>
     <t>GRDU</t>
   </si>
   <si>
@@ -897,10 +861,40 @@
     <t>XMME (EM, unhedged) - india 18%</t>
   </si>
   <si>
-    <t>China Robotics (2807.HK)</t>
-  </si>
-  <si>
     <t>China CSI300 (82846)</t>
+  </si>
+  <si>
+    <t>China Robotics (9807.HK)</t>
+  </si>
+  <si>
+    <t>EQCH (QQQ, hedged)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBUK (CQQQ, unhedged) </t>
+  </si>
+  <si>
+    <t>VWRA (VT, incl. EM)</t>
+  </si>
+  <si>
+    <t>Portfolio</t>
+  </si>
+  <si>
+    <t>The Vault (GSD, Gold)</t>
+  </si>
+  <si>
+    <t>Senior Tier-1 Gold Producer. Canada-based global miner with major operations in Canada (Detour Lake, Canadian Malartic), Australia (Fosterville), and Finland (Kittila).</t>
+  </si>
+  <si>
+    <t>AEM</t>
+  </si>
+  <si>
+    <t>Low-Risk Jurisdictions &amp; High Margins. Focuses on politically stable regions (Canada/Australia) to avoid resource nationalism. Boasts record-level profit margins (37.5%) and some of the industry's lowest All-In Sustaining Costs (AISC), ensuring profitability even if gold prices soften.</t>
+  </si>
+  <si>
+    <t>Stable Gold Exposure &amp; Dividend Income. Ideal for "Buy and Hold" investors seeking safe-haven assets with consistent income; has paid a dividend every year since 1983.</t>
+  </si>
+  <si>
+    <t>Bullish Growth. Median 12-month analyst price target is approximately $250.50, with high-end bull cases reaching $312 – $333 following a surge in gold prices to over $5,000/oz in early 2026.</t>
   </si>
 </sst>
 </file>
@@ -914,7 +908,7 @@
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1035,6 +1029,12 @@
       <name val="Consolas"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <name val="Consolas"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1045,12 +1045,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFFD78"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1166,6 +1166,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1173,7 +1184,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1228,10 +1239,6 @@
       <alignment horizontal="left" indent="4"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1259,11 +1266,28 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1425,9 +1449,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFD78"/>
       <color rgb="FFFF7E79"/>
       <color rgb="FFFF2600"/>
-      <color rgb="FFFFFD78"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1565,7 +1589,7 @@
                   <c:v>The Omega (insurance, SPY and QQQ bear spreads)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>The Vault (Gold)</c:v>
+                  <c:v>The Vault (GSD, Gold)</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>The War Chest (Cash)</c:v>
@@ -1580,25 +1604,25 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>502604.56847499998</c:v>
+                  <c:v>386878.51496000006</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>201041.82738999999</c:v>
+                  <c:v>193439.25748000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>201041.82738999999</c:v>
+                  <c:v>145079.44310999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>30156.274108499998</c:v>
+                  <c:v>29015.888621999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20104.182739</c:v>
+                  <c:v>19343.925748000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50260.456847499998</c:v>
+                  <c:v>96719.628740000015</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50260.456847499998</c:v>
+                  <c:v>48359.814370000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1712,7 +1736,7 @@
                   <c:v>The Omega (insurance, SPY and QQQ bear spreads)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>The Vault (Gold)</c:v>
+                  <c:v>The Vault (GSD, Gold)</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>The War Chest (Cash)</c:v>
@@ -1727,25 +1751,25 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>385495.53649999999</c:v>
+                  <c:v>373713.701</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>212281.10440000001</c:v>
+                  <c:v>108299.20439999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>104807.22</c:v>
+                  <c:v>94368.72</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14637.170000000056</c:v>
+                  <c:v>41219.992000000086</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13792.48</c:v>
+                  <c:v>17401.84</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46333.246050000002</c:v>
+                  <c:v>82398.81</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>227862.38</c:v>
+                  <c:v>249794.02000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2178,10 +2202,10 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.77331843531448707</c:v>
+                  <c:v>0.74173389284661972</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2266815646855129</c:v>
+                  <c:v>0.25826610715338028</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2655,7 +2679,7 @@
                   <c:v>SGD</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>CNH</c:v>
+                  <c:v>CNY</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2667,19 +2691,19 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>365115.64</c:v>
+                  <c:v>392933.95200000011</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>127769.98974999999</c:v>
+                  <c:v>116320.94839999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>99402.54</c:v>
+                  <c:v>51433.584999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>70588.302949999998</c:v>
+                  <c:v>150209.20199999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18152.184000000001</c:v>
+                  <c:v>22748.080000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2780,15 +2804,39 @@
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2800,15 +2848,39 @@
             <c:idx val="1"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2820,15 +2892,39 @@
             <c:idx val="2"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2840,17 +2936,42 @@
             <c:idx val="3"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2862,17 +2983,42 @@
             <c:idx val="4"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2884,17 +3030,42 @@
             <c:idx val="5"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2906,18 +3077,45 @@
             <c:idx val="6"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2929,18 +3127,45 @@
             <c:idx val="7"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2952,18 +3177,45 @@
             <c:idx val="8"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:lumOff val="20000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2975,17 +3227,42 @@
             <c:idx val="9"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2997,17 +3274,42 @@
             <c:idx val="10"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3019,17 +3321,42 @@
             <c:idx val="11"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="80000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="80000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3041,18 +3368,45 @@
             <c:idx val="12"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3064,18 +3418,45 @@
             <c:idx val="13"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3087,18 +3468,45 @@
             <c:idx val="14"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3110,17 +3518,42 @@
             <c:idx val="15"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="50000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="50000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="50000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3132,17 +3565,42 @@
             <c:idx val="16"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="50000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="50000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="50000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3154,17 +3612,42 @@
             <c:idx val="17"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="50000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="50000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent5">
+                      <a:lumMod val="50000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3176,18 +3659,45 @@
             <c:idx val="18"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="70000"/>
+                      <a:lumOff val="30000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="70000"/>
+                      <a:lumOff val="30000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent1">
+                      <a:lumMod val="70000"/>
+                      <a:lumOff val="30000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3199,18 +3709,45 @@
             <c:idx val="19"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="70000"/>
-                  <a:lumOff val="30000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="19050">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="70000"/>
+                      <a:lumOff val="30000"/>
+                      <a:shade val="51000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="80000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="70000"/>
+                      <a:lumOff val="30000"/>
+                      <a:shade val="93000"/>
+                      <a:satMod val="130000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent3">
+                      <a:lumMod val="70000"/>
+                      <a:lumOff val="30000"/>
+                      <a:shade val="94000"/>
+                      <a:satMod val="135000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="16200000" scaled="0"/>
+              </a:gradFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="35000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -3221,12 +3758,6 @@
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.21761658031088082"/>
-                  <c:y val="8.15450643776824E-2"/>
-                </c:manualLayout>
-              </c:layout>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -3241,7 +3772,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="bg1"/>
                       </a:solidFill>
@@ -3255,20 +3786,12 @@
               </c:txPr>
               <c:dLblPos val="bestFit"/>
               <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
               <c:showCatName val="1"/>
               <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
+              <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout>
-                    <c:manualLayout>
-                      <c:w val="0.24898100172711571"/>
-                      <c:h val="0.11763948497854078"/>
-                    </c:manualLayout>
-                  </c15:layout>
-                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-5B79-724A-AB6E-048CA154099D}"/>
                 </c:ext>
@@ -3276,12 +3799,6 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="7"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-3.6269294058449947E-2"/>
-                  <c:y val="-0.1630901287553648"/>
-                </c:manualLayout>
-              </c:layout>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -3296,7 +3813,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="bg1"/>
                       </a:solidFill>
@@ -3310,20 +3827,12 @@
               </c:txPr>
               <c:dLblPos val="bestFit"/>
               <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
               <c:showCatName val="1"/>
               <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
+              <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout>
-                    <c:manualLayout>
-                      <c:w val="0.26542314335060446"/>
-                      <c:h val="0.11763948497854078"/>
-                    </c:manualLayout>
-                  </c15:layout>
-                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-5B79-724A-AB6E-048CA154099D}"/>
                 </c:ext>
@@ -3331,10 +3840,102 @@
             </c:dLbl>
             <c:dLbl>
               <c:idx val="15"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="bg1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-5B79-724A-AB6E-048CA154099D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="16"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="1.2052137550602785E-2"/>
-                  <c:y val="-4.7210300429184469E-2"/>
+                  <c:x val="-1.3139152097513235E-2"/>
+                  <c:y val="5.9170355851441314E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-5B79-724A-AB6E-048CA154099D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="17"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.3803772409804706E-2"/>
+                  <c:y val="-5.7705045453009364E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.17521175319186796"/>
+                      <c:h val="0.1229184549356223"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-5B79-724A-AB6E-048CA154099D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="18"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.15677966101694915"/>
+                  <c:y val="8.3082694062383833E-3"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr>
@@ -3351,12 +3952,9 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="75000"/>
-                          <a:lumOff val="25000"/>
-                        </a:schemeClr>
+                        <a:schemeClr val="bg1"/>
                       </a:solidFill>
                       <a:latin typeface="+mn-lt"/>
                       <a:ea typeface="+mn-ea"/>
@@ -3368,149 +3966,27 @@
               </c:txPr>
               <c:dLblPos val="bestFit"/>
               <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
               <c:showCatName val="1"/>
               <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
+              <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout>
                     <c:manualLayout>
-                      <c:w val="0.2436443501557124"/>
-                      <c:h val="8.141630901287554E-2"/>
+                      <c:w val="0.12076271186440678"/>
+                      <c:h val="0.14377682403433475"/>
                     </c:manualLayout>
                   </c15:layout>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-5B79-724A-AB6E-048CA154099D}"/>
+                  <c16:uniqueId val="{00000004-5B79-724A-AB6E-048CA154099D}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
-              <c:idx val="16"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="3.184416566573246E-3"/>
-                  <c:y val="1.7109594133351277E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:noAutofit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="75000"/>
-                          <a:lumOff val="25000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout>
-                    <c:manualLayout>
-                      <c:w val="0.27663196091452424"/>
-                      <c:h val="7.4721030042918454E-2"/>
-                    </c:manualLayout>
-                  </c15:layout>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-5B79-724A-AB6E-048CA154099D}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="17"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="1.0442991708264583E-7"/>
-                  <c:y val="-1.9313135750735101E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:noAutofit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="75000"/>
-                          <a:lumOff val="25000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout>
-                    <c:manualLayout>
-                      <c:w val="0.26953372545299309"/>
-                      <c:h val="8.5708154506437761E-2"/>
-                    </c:manualLayout>
-                  </c15:layout>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-5B79-724A-AB6E-048CA154099D}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="18"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.18072289156626506"/>
-                  <c:y val="-4.2918454935622317E-3"/>
-                </c:manualLayout>
-              </c:layout>
+              <c:idx val="19"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -3525,7 +4001,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="bg1"/>
                       </a:solidFill>
@@ -3539,68 +4015,12 @@
               </c:txPr>
               <c:dLblPos val="bestFit"/>
               <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
+              <c:showVal val="0"/>
               <c:showCatName val="1"/>
               <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
+              <c:showPercent val="1"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-5B79-724A-AB6E-048CA154099D}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="19"/>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="0.17789319081228835"/>
-                  <c:y val="0.20600858369098712"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="bg1"/>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout>
-                    <c:manualLayout>
-                      <c:w val="0.22556131260794474"/>
-                      <c:h val="0.11763948497854078"/>
-                    </c:manualLayout>
-                  </c15:layout>
-                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000001-5B79-724A-AB6E-048CA154099D}"/>
                 </c:ext>
@@ -3620,12 +4040,9 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
+                      <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3635,12 +4052,12 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
+            <c:dLblPos val="bestFit"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="1"/>
             <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
+            <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
             <c:extLst>
@@ -3683,25 +4100,25 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.38349784371207413</c:v>
+                  <c:v>0.38638868435342177</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.21118103347538422</c:v>
+                  <c:v>0.11197231194003855</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.10426409405509932</c:v>
+                  <c:v>9.7569357150532832E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.4561318099845448E-2</c:v>
+                  <c:v>4.2618021323062499E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.3721005403760124E-2</c:v>
+                  <c:v>1.799204590288422E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.6093140568324004E-2</c:v>
+                  <c:v>8.5193472176679899E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.2266815646855129</c:v>
+                  <c:v>0.25826610715338028</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3713,6 +4130,7 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -3748,7 +4166,7 @@
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="tx2">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -5417,33 +5835,27 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="255">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -5458,7 +5870,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -5466,7 +5878,7 @@
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -5481,10 +5893,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
@@ -5493,9 +5902,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
@@ -5518,49 +5926,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="31750" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -5569,33 +5963,32 @@
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="12700">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="lt2"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -5611,21 +6004,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -5635,23 +6023,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -5660,17 +6047,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -5679,14 +6066,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -5698,26 +6084,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="tx2">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -5731,96 +6111,99 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -5828,17 +6211,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -5847,12 +6230,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -5861,14 +6241,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
+        <a:prstDash val="sysDash"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -5877,10 +6257,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
@@ -5889,20 +6266,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -5911,10 +6287,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="tx2"/>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
@@ -5923,14 +6296,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -6053,8 +6420,8 @@
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>2540000</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>1435100</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>190500</xdr:rowOff>
     </xdr:to>
@@ -6117,7 +6484,7 @@
             <v>EQCH</v>
           </cell>
           <cell r="V2">
-            <v>25722.762999999999</v>
+            <v>19729.850399999999</v>
           </cell>
         </row>
         <row r="3">
@@ -6125,10 +6492,10 @@
             <v>STK</v>
           </cell>
           <cell r="F3" t="str">
-            <v>WORLD</v>
+            <v>XMME</v>
           </cell>
           <cell r="V3">
-            <v>34494.157499999987</v>
+            <v>19633.185000000001</v>
           </cell>
         </row>
         <row r="4">
@@ -6136,10 +6503,10 @@
             <v>STK</v>
           </cell>
           <cell r="F4" t="str">
-            <v>XMME</v>
+            <v>82846</v>
           </cell>
           <cell r="V4">
-            <v>25692.466799999998</v>
+            <v>13648.848</v>
           </cell>
         </row>
         <row r="5">
@@ -6147,10 +6514,10 @@
             <v>STK</v>
           </cell>
           <cell r="F5" t="str">
-            <v>82846</v>
+            <v>CBUK</v>
           </cell>
           <cell r="V5">
-            <v>13657.116</v>
+            <v>9923.6563999999998</v>
           </cell>
         </row>
         <row r="6">
@@ -6158,10 +6525,10 @@
             <v>STK</v>
           </cell>
           <cell r="F6" t="str">
-            <v>CBUK</v>
+            <v>HY9H</v>
           </cell>
           <cell r="V6">
-            <v>20772.2592</v>
+            <v>9110.7659999999996</v>
           </cell>
         </row>
         <row r="7">
@@ -6172,7 +6539,7 @@
             <v>ES3</v>
           </cell>
           <cell r="V7">
-            <v>31638.751199999999</v>
+            <v>30137.952000000001</v>
           </cell>
         </row>
         <row r="8">
@@ -6183,7 +6550,7 @@
             <v>GSD</v>
           </cell>
           <cell r="V8">
-            <v>23166.623025000001</v>
+            <v>34973.205000000002</v>
           </cell>
         </row>
         <row r="9">
@@ -6191,10 +6558,10 @@
             <v>STK</v>
           </cell>
           <cell r="F9" t="str">
-            <v>BITO</v>
+            <v>9807</v>
           </cell>
           <cell r="V9">
-            <v>936</v>
+            <v>7735</v>
           </cell>
         </row>
         <row r="10">
@@ -6202,10 +6569,10 @@
             <v>STK</v>
           </cell>
           <cell r="F10" t="str">
-            <v>CELH</v>
+            <v>AEM</v>
           </cell>
           <cell r="V10">
-            <v>2416</v>
+            <v>6226.2</v>
           </cell>
         </row>
         <row r="11">
@@ -6213,10 +6580,10 @@
             <v>STK</v>
           </cell>
           <cell r="F11" t="str">
-            <v>CHA</v>
+            <v>BITO</v>
           </cell>
           <cell r="V11">
-            <v>1034</v>
+            <v>980</v>
           </cell>
         </row>
         <row r="12">
@@ -6224,10 +6591,10 @@
             <v>STK</v>
           </cell>
           <cell r="F12" t="str">
-            <v>CSNDX</v>
+            <v>GOOGL</v>
           </cell>
           <cell r="V12">
-            <v>21465</v>
+            <v>30228</v>
           </cell>
         </row>
         <row r="13">
@@ -6235,10 +6602,10 @@
             <v>STK</v>
           </cell>
           <cell r="F13" t="str">
-            <v>GOOGL</v>
+            <v>GRDU</v>
           </cell>
           <cell r="V13">
-            <v>31498</v>
+            <v>9113.6</v>
           </cell>
         </row>
         <row r="14">
@@ -6246,10 +6613,10 @@
             <v>STK</v>
           </cell>
           <cell r="F14" t="str">
-            <v>GRDU</v>
+            <v>INRA</v>
           </cell>
           <cell r="V14">
-            <v>4860</v>
+            <v>10435.35</v>
           </cell>
         </row>
         <row r="15">
@@ -6257,10 +6624,10 @@
             <v>STK</v>
           </cell>
           <cell r="F15" t="str">
-            <v>HEAL</v>
+            <v>ORCL</v>
           </cell>
           <cell r="V15">
-            <v>9140</v>
+            <v>10857.7</v>
           </cell>
         </row>
         <row r="16">
@@ -6268,10 +6635,10 @@
             <v>STK</v>
           </cell>
           <cell r="F16" t="str">
-            <v>INRA</v>
+            <v>SE</v>
           </cell>
           <cell r="V16">
-            <v>10733.03</v>
+            <v>1720</v>
           </cell>
         </row>
         <row r="17">
@@ -6279,54 +6646,54 @@
             <v>STK</v>
           </cell>
           <cell r="F17" t="str">
-            <v>LKNCY</v>
+            <v>VWRA</v>
           </cell>
           <cell r="V17">
-            <v>3890</v>
+            <v>83910</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18" t="str">
-            <v>STK</v>
+            <v>OPT</v>
           </cell>
           <cell r="F18" t="str">
-            <v>LOCK</v>
+            <v>AAPL  260327C00290000</v>
           </cell>
           <cell r="V18">
-            <v>9870</v>
+            <v>2.5499999999999998</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19" t="str">
-            <v>STK</v>
+            <v>OPT</v>
           </cell>
           <cell r="F19" t="str">
-            <v>ORCL</v>
+            <v>MSFT  260327C00420000</v>
           </cell>
           <cell r="V19">
-            <v>14808</v>
+            <v>123.5</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20" t="str">
-            <v>STK</v>
+            <v>OPT</v>
           </cell>
           <cell r="F20" t="str">
-            <v>SE</v>
+            <v>QQQ   261218P00560000</v>
           </cell>
           <cell r="V20">
-            <v>2300</v>
+            <v>6825</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21" t="str">
-            <v>STK</v>
+            <v>OPT</v>
           </cell>
           <cell r="F21" t="str">
-            <v>VWRA</v>
+            <v>SPY   261218P00620000</v>
           </cell>
           <cell r="V21">
-            <v>35320</v>
+            <v>5974</v>
           </cell>
         </row>
         <row r="22">
@@ -6334,10 +6701,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F22" t="str">
-            <v>QQQ   261218P00560000</v>
+            <v>AAPL  260327P00250000</v>
           </cell>
           <cell r="V22">
-            <v>5729.78</v>
+            <v>-575</v>
           </cell>
         </row>
         <row r="23">
@@ -6345,10 +6712,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F23" t="str">
-            <v>SPY   261218P00620000</v>
+            <v>AAPL  260327C00285000</v>
           </cell>
           <cell r="V23">
-            <v>4307.18</v>
+            <v>-5.42</v>
           </cell>
         </row>
         <row r="24">
@@ -6356,10 +6723,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F24" t="str">
-            <v>GOOGL 260306C00325000</v>
+            <v>AMD   260327P00185000</v>
           </cell>
           <cell r="V24">
-            <v>-375</v>
+            <v>-507.5</v>
           </cell>
         </row>
         <row r="25">
@@ -6367,10 +6734,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F25" t="str">
-            <v>GOOGL 260327P00300000</v>
+            <v>AMZN  260327P00190000</v>
           </cell>
           <cell r="V25">
-            <v>-635</v>
+            <v>-135</v>
           </cell>
         </row>
         <row r="26">
@@ -6378,10 +6745,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F26" t="str">
-            <v>IWM   260227P00257000</v>
+            <v>AMZN  260327C00235000</v>
           </cell>
           <cell r="V26">
-            <v>-234</v>
+            <v>-15.5</v>
           </cell>
         </row>
         <row r="27">
@@ -6389,10 +6756,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F27" t="str">
-            <v>IWM   260227C00277000</v>
+            <v>GOOGL 260327P00295000</v>
           </cell>
           <cell r="V27">
-            <v>-15</v>
+            <v>-965</v>
           </cell>
         </row>
         <row r="28">
@@ -6400,10 +6767,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F28" t="str">
-            <v>NVDA  260227P00175000</v>
+            <v>GOOGL 260327C00315000</v>
           </cell>
           <cell r="V28">
-            <v>-301</v>
+            <v>-263.5</v>
           </cell>
         </row>
         <row r="29">
@@ -6411,10 +6778,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F29" t="str">
-            <v>ORCL  260227P00140000</v>
+            <v>MSFT  260327P00360000</v>
           </cell>
           <cell r="V29">
-            <v>-246.5</v>
+            <v>-122</v>
           </cell>
         </row>
         <row r="30">
@@ -6422,10 +6789,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F30" t="str">
-            <v>ORCL  260306C00165000</v>
+            <v>MSFT  260327C00415000</v>
           </cell>
           <cell r="V30">
-            <v>-167</v>
+            <v>-202</v>
           </cell>
         </row>
         <row r="31">
@@ -6433,10 +6800,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F31" t="str">
-            <v>QQQ   261218P00425000</v>
+            <v>NFLX  260327P00088000</v>
           </cell>
           <cell r="V31">
-            <v>-1561.72</v>
+            <v>-110</v>
           </cell>
         </row>
         <row r="32">
@@ -6444,10 +6811,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F32" t="str">
-            <v>SMH   260227P00377500</v>
+            <v>QQQ   261218P00425000</v>
           </cell>
           <cell r="V32">
-            <v>-290.22000000000003</v>
+            <v>-1939.08</v>
           </cell>
         </row>
         <row r="33">
@@ -6455,21 +6822,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F33" t="str">
-            <v>SMH   260227C00437500</v>
+            <v>SPY   261218P00505000</v>
           </cell>
           <cell r="V33">
-            <v>-352</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="D34" t="str">
-            <v>OPT</v>
-          </cell>
-          <cell r="F34" t="str">
-            <v>SPY   261218P00505000</v>
-          </cell>
-          <cell r="V34">
-            <v>-1579</v>
+            <v>-2159</v>
           </cell>
         </row>
       </sheetData>
@@ -6493,7 +6849,7 @@
             <v>EQCH</v>
           </cell>
           <cell r="V2">
-            <v>25722.762999999999</v>
+            <v>24662.312999999998</v>
           </cell>
         </row>
         <row r="3">
@@ -6501,10 +6857,10 @@
             <v>STK</v>
           </cell>
           <cell r="F3" t="str">
-            <v>WORLD</v>
+            <v>XMME</v>
           </cell>
           <cell r="V3">
-            <v>41392.988999999987</v>
+            <v>27486.458999999999</v>
           </cell>
         </row>
         <row r="4">
@@ -6512,10 +6868,10 @@
             <v>STK</v>
           </cell>
           <cell r="F4" t="str">
-            <v>XMME</v>
+            <v>82846</v>
           </cell>
           <cell r="V4">
-            <v>42820.777999999998</v>
+            <v>9099.232</v>
           </cell>
         </row>
         <row r="5">
@@ -6523,10 +6879,10 @@
             <v>STK</v>
           </cell>
           <cell r="F5" t="str">
-            <v>82846</v>
+            <v>CBUK</v>
           </cell>
           <cell r="V5">
-            <v>9104.7440000000006</v>
+            <v>14885.4846</v>
           </cell>
         </row>
         <row r="6">
@@ -6534,10 +6890,10 @@
             <v>STK</v>
           </cell>
           <cell r="F6" t="str">
-            <v>CBUK</v>
+            <v>DHL</v>
           </cell>
           <cell r="V6">
-            <v>20772.2592</v>
+            <v>51433.584999999999</v>
           </cell>
         </row>
         <row r="7">
@@ -6545,10 +6901,10 @@
             <v>STK</v>
           </cell>
           <cell r="F7" t="str">
-            <v>DHL</v>
+            <v>HY9H</v>
           </cell>
           <cell r="V7">
-            <v>58846.094999999987</v>
+            <v>9110.7659999999996</v>
           </cell>
         </row>
         <row r="8">
@@ -6559,7 +6915,7 @@
             <v>ES3</v>
           </cell>
           <cell r="V8">
-            <v>39548.438999999998</v>
+            <v>37672.44</v>
           </cell>
         </row>
         <row r="9">
@@ -6570,7 +6926,7 @@
             <v>GSD</v>
           </cell>
           <cell r="V9">
-            <v>23166.623025000001</v>
+            <v>34973.205000000002</v>
           </cell>
         </row>
         <row r="10">
@@ -6578,10 +6934,10 @@
             <v>STK</v>
           </cell>
           <cell r="F10" t="str">
-            <v>BITO</v>
+            <v>9807</v>
           </cell>
           <cell r="V10">
-            <v>2808</v>
+            <v>8508.5</v>
           </cell>
         </row>
         <row r="11">
@@ -6589,10 +6945,10 @@
             <v>STK</v>
           </cell>
           <cell r="F11" t="str">
-            <v>CSNDX</v>
+            <v>AEM</v>
           </cell>
           <cell r="V11">
-            <v>28620</v>
+            <v>6226.2</v>
           </cell>
         </row>
         <row r="12">
@@ -6600,10 +6956,10 @@
             <v>STK</v>
           </cell>
           <cell r="F12" t="str">
-            <v>GOOGL</v>
+            <v>BITO</v>
           </cell>
           <cell r="V12">
-            <v>31498</v>
+            <v>2940</v>
           </cell>
         </row>
         <row r="13">
@@ -6611,10 +6967,10 @@
             <v>STK</v>
           </cell>
           <cell r="F13" t="str">
-            <v>GRDU</v>
+            <v>GOOGL</v>
           </cell>
           <cell r="V13">
-            <v>4860</v>
+            <v>30228</v>
           </cell>
         </row>
         <row r="14">
@@ -6622,10 +6978,10 @@
             <v>STK</v>
           </cell>
           <cell r="F14" t="str">
-            <v>HEAL</v>
+            <v>GRDU</v>
           </cell>
           <cell r="V14">
-            <v>9140</v>
+            <v>9113.6</v>
           </cell>
         </row>
         <row r="15">
@@ -6636,7 +6992,7 @@
             <v>IBKR</v>
           </cell>
           <cell r="V15">
-            <v>1253.17</v>
+            <v>1114.96</v>
           </cell>
         </row>
         <row r="16">
@@ -6647,7 +7003,7 @@
             <v>INRA</v>
           </cell>
           <cell r="V16">
-            <v>10733.03</v>
+            <v>10435.35</v>
           </cell>
         </row>
         <row r="17">
@@ -6658,7 +7014,7 @@
             <v>JPM</v>
           </cell>
           <cell r="V17">
-            <v>31079</v>
+            <v>28344</v>
           </cell>
         </row>
         <row r="18">
@@ -6666,21 +7022,21 @@
             <v>STK</v>
           </cell>
           <cell r="F18" t="str">
-            <v>LOCK</v>
+            <v>VWRA</v>
           </cell>
           <cell r="V18">
-            <v>9870</v>
+            <v>100692</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19" t="str">
-            <v>STK</v>
+            <v>OPT</v>
           </cell>
           <cell r="F19" t="str">
-            <v>VWRA</v>
+            <v>AAPL  260327C00290000</v>
           </cell>
           <cell r="V19">
-            <v>52980</v>
+            <v>2.5499999999999998</v>
           </cell>
         </row>
         <row r="20">
@@ -6688,10 +7044,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F20" t="str">
-            <v>QQQ   261218P00560000</v>
+            <v>NFLX  260327C00085000</v>
           </cell>
           <cell r="V20">
-            <v>5729.78</v>
+            <v>1077.6400000000001</v>
           </cell>
         </row>
         <row r="21">
@@ -6699,10 +7055,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F21" t="str">
-            <v>SPY   261218P00620000</v>
+            <v>QQQ   261218P00560000</v>
           </cell>
           <cell r="V21">
-            <v>4307.18</v>
+            <v>6825</v>
           </cell>
         </row>
         <row r="22">
@@ -6710,10 +7066,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F22" t="str">
-            <v>GOOGL 260304P00295000</v>
+            <v>SPY   261218P00620000</v>
           </cell>
           <cell r="V22">
-            <v>-140.91</v>
+            <v>5974</v>
           </cell>
         </row>
         <row r="23">
@@ -6721,10 +7077,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F23" t="str">
-            <v>IWM   260227P00257000</v>
+            <v>AAPL  260327P00250000</v>
           </cell>
           <cell r="V23">
-            <v>-234</v>
+            <v>-575</v>
           </cell>
         </row>
         <row r="24">
@@ -6732,10 +7088,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F24" t="str">
-            <v>IWM   260227C00277000</v>
+            <v>AAPL  260327C00285000</v>
           </cell>
           <cell r="V24">
-            <v>-15</v>
+            <v>-5.42</v>
           </cell>
         </row>
         <row r="25">
@@ -6743,10 +7099,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F25" t="str">
-            <v>JPM   260327C00325000</v>
+            <v>AMD   260327P00185000</v>
           </cell>
           <cell r="V25">
-            <v>-427.93</v>
+            <v>-507.5</v>
           </cell>
         </row>
         <row r="26">
@@ -6754,10 +7110,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F26" t="str">
-            <v>QQQ   261218P00425000</v>
+            <v>AMD   260327C00255000</v>
           </cell>
           <cell r="V26">
-            <v>-1561.72</v>
+            <v>-6.5</v>
           </cell>
         </row>
         <row r="27">
@@ -6765,10 +7121,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F27" t="str">
-            <v>SMH   260227P00377500</v>
+            <v>AMZN  260327P00190000</v>
           </cell>
           <cell r="V27">
-            <v>-290.22000000000003</v>
+            <v>-135</v>
           </cell>
         </row>
         <row r="28">
@@ -6776,10 +7132,10 @@
             <v>OPT</v>
           </cell>
           <cell r="F28" t="str">
-            <v>SMH   260227C00437500</v>
+            <v>GOOGL 260327P00295000</v>
           </cell>
           <cell r="V28">
-            <v>-352</v>
+            <v>-482.5</v>
           </cell>
         </row>
         <row r="29">
@@ -6787,22 +7143,88 @@
             <v>OPT</v>
           </cell>
           <cell r="F29" t="str">
+            <v>GOOGL 260327C00315000</v>
+          </cell>
+          <cell r="V29">
+            <v>-263.5</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="D30" t="str">
+            <v>OPT</v>
+          </cell>
+          <cell r="F30" t="str">
+            <v>JPM   260327C00297500</v>
+          </cell>
+          <cell r="V30">
+            <v>-226</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="D31" t="str">
+            <v>OPT</v>
+          </cell>
+          <cell r="F31" t="str">
+            <v>MSFT  260327P00360000</v>
+          </cell>
+          <cell r="V31">
+            <v>-122</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="D32" t="str">
+            <v>OPT</v>
+          </cell>
+          <cell r="F32" t="str">
+            <v>NFLX  260327P00072000</v>
+          </cell>
+          <cell r="V32">
+            <v>-2.89</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="D33" t="str">
+            <v>OPT</v>
+          </cell>
+          <cell r="F33" t="str">
+            <v>NFLX  260327C00083000</v>
+          </cell>
+          <cell r="V33">
+            <v>-1267.99</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="D34" t="str">
+            <v>OPT</v>
+          </cell>
+          <cell r="F34" t="str">
+            <v>QQQ   261218P00425000</v>
+          </cell>
+          <cell r="V34">
+            <v>-1939.08</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="D35" t="str">
+            <v>OPT</v>
+          </cell>
+          <cell r="F35" t="str">
             <v>SPY   261218P00505000</v>
           </cell>
-          <cell r="V29">
-            <v>-1579</v>
+          <cell r="V35">
+            <v>-2159</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="2">
         <row r="2">
           <cell r="C2" t="str">
-            <v>$114,463.22</v>
+            <v>$124,994.03</v>
           </cell>
         </row>
         <row r="3">
           <cell r="C3" t="str">
-            <v>$113,399.16</v>
+            <v>$124,799.99</v>
           </cell>
         </row>
       </sheetData>
@@ -7119,7 +7541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="38.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -7131,12 +7553,14 @@
     <col min="8" max="9" width="16.5" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="38.6640625" style="1"/>
+    <col min="12" max="12" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="38.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="33"/>
       <c r="E1" s="20" t="s">
         <v>0</v>
@@ -7149,8 +7573,9 @@
       <c r="K1" s="37"/>
       <c r="L1" s="37"/>
       <c r="M1" s="27"/>
+      <c r="O1" s="27"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="33" t="s">
         <v>2</v>
       </c>
@@ -7159,26 +7584,27 @@
       </c>
       <c r="E2" s="21">
         <f>F4+F11+F19+F22+F23+F20+F21</f>
-        <v>442157.90672500001</v>
+        <v>429283.39280000009</v>
       </c>
       <c r="F2" s="22"/>
       <c r="G2" s="28"/>
       <c r="H2" s="21">
         <f>I4+I11+I19+I22+I23+I20+I21</f>
-        <v>563051.23022499995</v>
+        <v>537912.8946</v>
       </c>
       <c r="I2" s="22"/>
       <c r="J2" s="28"/>
       <c r="K2" s="37"/>
       <c r="L2" s="37"/>
       <c r="M2" s="27"/>
+      <c r="O2" s="27"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="34" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>4</v>
@@ -7190,16 +7616,16 @@
         <v>5</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H3" s="23" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>7</v>
@@ -7207,121 +7633,135 @@
       <c r="K3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="57" t="s">
-        <v>190</v>
-      </c>
-      <c r="M3" s="58"/>
+      <c r="L3" s="64" t="s">
+        <v>180</v>
+      </c>
+      <c r="M3" s="65"/>
+      <c r="N3" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" s="65"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="35" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B4" s="42"/>
       <c r="C4" s="43">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D4" s="18">
         <f>$G$42*C4</f>
-        <v>502604.56847499998</v>
+        <v>386878.51496000006</v>
       </c>
       <c r="E4" s="24">
         <f>$E$2*C4</f>
-        <v>221078.9533625</v>
+        <v>171713.35712000006</v>
       </c>
       <c r="F4" s="18" cm="1">
         <f t="array" ref="F4">SUMPRODUCT(SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,GlobalETF!A:A))</f>
-        <v>140802.4915</v>
+        <v>147329.98500000002</v>
       </c>
       <c r="G4" s="30">
         <f>F4/E4</f>
-        <v>0.63688781477596457</v>
+        <v>0.85799956084394768</v>
       </c>
       <c r="H4" s="24">
         <f>$H$2*C4</f>
-        <v>281525.61511249997</v>
+        <v>215165.15784</v>
       </c>
       <c r="I4" s="18" cm="1">
         <f t="array" ref="I4">SUMPRODUCT(SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,GlobalETF!A:A))</f>
-        <v>244693.04499999998</v>
+        <v>226383.71599999999</v>
       </c>
       <c r="J4" s="30">
         <f>I4/H4</f>
-        <v>0.86916796150935893</v>
+        <v>1.0521392881292717</v>
       </c>
       <c r="K4" s="38">
-        <f t="shared" ref="K4:K23" si="0">F4+I4</f>
-        <v>385495.53649999999</v>
-      </c>
-      <c r="L4" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="M4" s="49">
+        <f t="shared" ref="K4" si="0">F4+I4</f>
+        <v>373713.701</v>
+      </c>
+      <c r="L4" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="M4" s="47">
         <f t="shared" ref="M4:M21" si="1">K4/$G$42</f>
-        <v>0.38349784371207413</v>
-      </c>
+        <v>0.38638868435342177</v>
+      </c>
+      <c r="N4" s="59"/>
+      <c r="O4" s="60"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="36" t="s">
-        <v>207</v>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="66" t="s">
+        <v>194</v>
       </c>
       <c r="B5" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="55">
         <v>0.05</v>
       </c>
       <c r="D5" s="19">
         <f>$D$4*C5</f>
-        <v>25130.228423749999</v>
+        <v>19343.925748000005</v>
       </c>
       <c r="E5" s="25">
         <f>$E$4*C5</f>
-        <v>11053.947668125002</v>
+        <v>8585.6678560000037</v>
       </c>
       <c r="F5" s="19">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"82846")</f>
-        <v>13657.116</v>
+        <v>13648.848</v>
       </c>
       <c r="G5" s="31">
         <f>F5/E5</f>
-        <v>1.2354967121276914</v>
+        <v>1.5897246701037528</v>
       </c>
       <c r="H5" s="25">
         <f>$H$4*C5</f>
-        <v>14076.280755624999</v>
+        <v>10758.257892000001</v>
       </c>
       <c r="I5" s="19">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"82846")</f>
-        <v>9104.7440000000006</v>
+        <v>9099.232</v>
       </c>
       <c r="J5" s="31">
         <f>I5/H5</f>
-        <v>0.64681460664683521</v>
+        <v>0.84579047010634711</v>
       </c>
       <c r="K5" s="39">
         <f t="shared" ref="K5:K7" si="2">F5+I5</f>
-        <v>22761.86</v>
-      </c>
-      <c r="L5" s="53"/>
-      <c r="M5" s="50"/>
+        <v>22748.080000000002</v>
+      </c>
+      <c r="L5" s="51"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="63">
+        <f>K5</f>
+        <v>22748.080000000002</v>
+      </c>
+      <c r="O5" s="27" t="str">
+        <f>B5</f>
+        <v>CNY</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="36" t="s">
-        <v>119</v>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="66" t="s">
+        <v>117</v>
       </c>
       <c r="B6" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="44">
-        <v>0.1</v>
+      <c r="C6" s="57">
+        <v>0.05</v>
       </c>
       <c r="D6" s="19">
         <f t="shared" ref="D6:D10" si="3">$D$4*C6</f>
-        <v>50260.456847499998</v>
+        <v>19343.925748000005</v>
       </c>
       <c r="E6" s="25">
         <f t="shared" ref="E6:E10" si="4">$E$4*C6</f>
-        <v>22107.895336250003</v>
+        <v>8585.6678560000037</v>
       </c>
       <c r="F6" s="19">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"DHL")</f>
@@ -7333,525 +7773,543 @@
       </c>
       <c r="H6" s="25">
         <f t="shared" ref="H6:H10" si="6">$H$4*C6</f>
-        <v>28152.561511249998</v>
+        <v>10758.257892000001</v>
       </c>
       <c r="I6" s="19">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"DHL")</f>
-        <v>58846.094999999987</v>
+        <v>51433.584999999999</v>
       </c>
       <c r="J6" s="31">
         <f t="shared" ref="J6:J7" si="7">I6/H6</f>
-        <v>2.0902572214071746</v>
+        <v>4.780847002956377</v>
       </c>
       <c r="K6" s="39">
         <f t="shared" si="2"/>
-        <v>58846.094999999987</v>
-      </c>
-      <c r="L6" s="53"/>
-      <c r="M6" s="50"/>
+        <v>51433.584999999999</v>
+      </c>
+      <c r="L6" s="51"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="63">
+        <f t="shared" ref="N6:N10" si="8">K6</f>
+        <v>51433.584999999999</v>
+      </c>
+      <c r="O6" s="27" t="str">
+        <f t="shared" ref="O6:O10" si="9">B6</f>
+        <v>EUR</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="36" t="s">
-        <v>120</v>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="66" t="s">
+        <v>118</v>
       </c>
       <c r="B7" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="44">
-        <v>0.1</v>
+      <c r="C7" s="57">
+        <v>0.05</v>
       </c>
       <c r="D7" s="19">
         <f t="shared" si="3"/>
-        <v>50260.456847499998</v>
+        <v>19343.925748000005</v>
       </c>
       <c r="E7" s="25">
         <f t="shared" si="4"/>
-        <v>22107.895336250003</v>
+        <v>8585.6678560000037</v>
       </c>
       <c r="F7" s="19">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"ES3")</f>
-        <v>31638.751199999999</v>
+        <v>30137.952000000001</v>
       </c>
       <c r="G7" s="31">
         <f t="shared" si="5"/>
-        <v>1.431106431380756</v>
+        <v>3.5102629760989892</v>
       </c>
       <c r="H7" s="25">
         <f t="shared" si="6"/>
-        <v>28152.561511249998</v>
+        <v>10758.257892000001</v>
       </c>
       <c r="I7" s="19">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"ES3")</f>
-        <v>39548.438999999998</v>
+        <v>37672.44</v>
       </c>
       <c r="J7" s="31">
         <f t="shared" si="7"/>
-        <v>1.4047900751125653</v>
+        <v>3.5017230836243276</v>
       </c>
       <c r="K7" s="39">
         <f t="shared" si="2"/>
-        <v>71187.190199999997</v>
-      </c>
-      <c r="L7" s="53"/>
-      <c r="M7" s="50"/>
+        <v>67810.392000000007</v>
+      </c>
+      <c r="L7" s="51"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="63">
+        <f t="shared" si="8"/>
+        <v>67810.392000000007</v>
+      </c>
+      <c r="O7" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>SGD</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="36" t="s">
-        <v>121</v>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="66" t="s">
+        <v>198</v>
       </c>
       <c r="B8" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="44">
-        <v>0.3</v>
+      <c r="C8" s="55">
+        <v>0.75</v>
       </c>
       <c r="D8" s="19">
         <f t="shared" si="3"/>
-        <v>150781.37054249999</v>
+        <v>290158.88622000004</v>
       </c>
       <c r="E8" s="25">
         <f t="shared" si="4"/>
-        <v>66323.686008749995</v>
+        <v>128785.01784000004</v>
       </c>
       <c r="F8" s="19">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"VWRA")</f>
-        <v>35320</v>
+        <v>83910</v>
       </c>
       <c r="G8" s="31">
         <f>F8/E8</f>
-        <v>0.53253976257200597</v>
+        <v>0.65155094441379913</v>
       </c>
       <c r="H8" s="25">
         <f t="shared" si="6"/>
-        <v>84457.684533749984</v>
+        <v>161373.86838</v>
       </c>
       <c r="I8" s="19">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"VWRA")</f>
-        <v>52980</v>
+        <v>100692</v>
       </c>
       <c r="J8" s="31">
-        <f>I8/H8</f>
-        <v>0.62729638270900923</v>
+        <f t="shared" ref="J8:J17" si="10">I8/H8</f>
+        <v>0.62396719500391762</v>
       </c>
       <c r="K8" s="39">
-        <f>F8+I8</f>
-        <v>88300</v>
-      </c>
-      <c r="L8" s="53"/>
-      <c r="M8" s="50"/>
+        <f t="shared" ref="K8:K17" si="11">F8+I8</f>
+        <v>184602</v>
+      </c>
+      <c r="L8" s="51"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="63">
+        <f t="shared" si="8"/>
+        <v>184602</v>
+      </c>
+      <c r="O8" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>USD</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="44">
-        <v>0.3</v>
-      </c>
-      <c r="D9" s="19">
-        <f t="shared" ref="D9" si="8">$D$4*C9</f>
-        <v>150781.37054249999</v>
-      </c>
-      <c r="E9" s="25">
-        <f t="shared" ref="E9" si="9">$E$4*C9</f>
-        <v>66323.686008749995</v>
-      </c>
-      <c r="F9" s="19">
-        <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"WORLD")</f>
-        <v>34494.157499999987</v>
-      </c>
-      <c r="G9" s="31">
-        <f>F9/E9</f>
-        <v>0.52008806469907631</v>
-      </c>
-      <c r="H9" s="25">
-        <f t="shared" ref="H9" si="10">$H$4*C9</f>
-        <v>84457.684533749984</v>
-      </c>
-      <c r="I9" s="19">
-        <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"WORLD")</f>
-        <v>41392.988999999987</v>
-      </c>
-      <c r="J9" s="31">
-        <f>I9/H9</f>
-        <v>0.49010328933963387</v>
-      </c>
-      <c r="K9" s="39">
-        <f>F9+I9</f>
-        <v>75887.146499999973</v>
-      </c>
-      <c r="L9" s="53"/>
-      <c r="M9" s="50"/>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="36"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="27"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="36" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="44">
-        <v>0.15</v>
+        <v>125</v>
+      </c>
+      <c r="C10" s="55">
+        <v>0.1</v>
       </c>
       <c r="D10" s="19">
         <f t="shared" si="3"/>
-        <v>75390.685271249997</v>
+        <v>38687.85149600001</v>
       </c>
       <c r="E10" s="25">
         <f t="shared" si="4"/>
-        <v>33161.843004374998</v>
+        <v>17171.335712000007</v>
       </c>
       <c r="F10" s="19">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"XMME")</f>
-        <v>25692.466799999998</v>
+        <v>19633.185000000001</v>
       </c>
       <c r="G10" s="31">
         <f>F10/E10</f>
-        <v>0.77475991900119745</v>
+        <v>1.1433697022346117</v>
       </c>
       <c r="H10" s="25">
         <f t="shared" si="6"/>
-        <v>42228.842266874992</v>
+        <v>21516.515784000003</v>
       </c>
       <c r="I10" s="19">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"XMME")</f>
-        <v>42820.777999999998</v>
+        <v>27486.458999999999</v>
       </c>
       <c r="J10" s="31">
-        <f>I10/H10</f>
-        <v>1.0140173327363353</v>
+        <f t="shared" si="10"/>
+        <v>1.2774586404198087</v>
       </c>
       <c r="K10" s="39">
-        <f>F10+I10</f>
-        <v>68513.2448</v>
-      </c>
-      <c r="L10" s="53"/>
-      <c r="M10" s="50"/>
+        <f t="shared" si="11"/>
+        <v>47119.644</v>
+      </c>
+      <c r="L10" s="51"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="63">
+        <f t="shared" si="8"/>
+        <v>47119.644</v>
+      </c>
+      <c r="O10" s="27" t="str">
+        <f t="shared" si="9"/>
+        <v>CHF</v>
+      </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="35" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B11" s="42"/>
-      <c r="C11" s="43">
+      <c r="C11" s="56">
         <v>0.2</v>
       </c>
       <c r="D11" s="18">
         <f>$G$42*C11</f>
-        <v>201041.82738999999</v>
+        <v>193439.25748000003</v>
       </c>
       <c r="E11" s="24">
         <f>$E$2*C11</f>
-        <v>88431.581345000013</v>
+        <v>85856.678560000029</v>
       </c>
       <c r="F11" s="18" cm="1">
         <f t="array" ref="F11">SUMPRODUCT(SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,GrowthEngine!A:A))</f>
-        <v>102563.05220000001</v>
+        <v>49202.4568</v>
       </c>
       <c r="G11" s="30">
         <f>F11/E11</f>
-        <v>1.1598011778152941</v>
+        <v>0.57307663917624518</v>
       </c>
       <c r="H11" s="24">
         <f>$H$2*C11</f>
-        <v>112610.24604499999</v>
+        <v>107582.57892</v>
       </c>
       <c r="I11" s="18" cm="1">
         <f t="array" ref="I11">SUMPRODUCT(SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,GrowthEngine!A:A))</f>
-        <v>109718.05220000001</v>
+        <v>59096.747599999995</v>
       </c>
       <c r="J11" s="30">
-        <f>I11/H11</f>
-        <v>0.9743167789204169</v>
+        <f t="shared" si="10"/>
+        <v>0.54931521621121593</v>
       </c>
       <c r="K11" s="38">
-        <f>F11+I11</f>
-        <v>212281.10440000001</v>
-      </c>
-      <c r="L11" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="M11" s="50">
+        <f t="shared" si="11"/>
+        <v>108299.20439999999</v>
+      </c>
+      <c r="L11" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="M11" s="48">
         <f t="shared" si="1"/>
-        <v>0.21118103347538422</v>
-      </c>
+        <v>0.11197231194003855</v>
+      </c>
+      <c r="N11" s="37"/>
+      <c r="O11" s="27"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="44">
-        <v>0.25</v>
-      </c>
-      <c r="D12" s="19">
-        <f t="shared" ref="D12:D17" si="11">$D$11*C12</f>
-        <v>50260.456847499998</v>
-      </c>
-      <c r="E12" s="25">
-        <f t="shared" ref="E12:E15" si="12">$E$11*C12</f>
-        <v>22107.895336250003</v>
-      </c>
-      <c r="F12" s="19">
-        <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"CSNDX")</f>
-        <v>21465</v>
-      </c>
-      <c r="G12" s="31">
-        <f>F12/E12</f>
-        <v>0.9709201022317191</v>
-      </c>
-      <c r="H12" s="25">
-        <f t="shared" ref="H12:H15" si="13">$H$11*C12</f>
-        <v>28152.561511249998</v>
-      </c>
-      <c r="I12" s="19">
-        <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"CSNDX")</f>
-        <v>28620</v>
-      </c>
-      <c r="J12" s="31">
-        <f>I12/H12</f>
-        <v>1.0166037640505008</v>
-      </c>
-      <c r="K12" s="39">
-        <f t="shared" si="0"/>
-        <v>50085</v>
-      </c>
-      <c r="L12" s="53"/>
-      <c r="M12" s="50"/>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="36"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="27"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="36" t="s">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="C13" s="44">
-        <v>0.25</v>
+        <v>125</v>
+      </c>
+      <c r="C13" s="55">
+        <v>0.6</v>
       </c>
       <c r="D13" s="19">
-        <f t="shared" si="11"/>
-        <v>50260.456847499998</v>
+        <f t="shared" ref="D12:D17" si="12">$D$11*C13</f>
+        <v>116063.55448800001</v>
       </c>
       <c r="E13" s="25">
-        <f t="shared" si="12"/>
-        <v>22107.895336250003</v>
+        <f t="shared" ref="E12:E15" si="13">$E$11*C13</f>
+        <v>51514.007136000015</v>
       </c>
       <c r="F13" s="19">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"EQCH")</f>
-        <v>25722.762999999999</v>
+        <v>19729.850399999999</v>
       </c>
       <c r="G13" s="31">
         <f t="shared" ref="G13:G15" si="14">F13/E13</f>
-        <v>1.1635102577052077</v>
+        <v>0.38299972176328723</v>
       </c>
       <c r="H13" s="25">
-        <f t="shared" si="13"/>
-        <v>28152.561511249998</v>
+        <f t="shared" ref="H12:H15" si="15">$H$11*C13</f>
+        <v>64549.547351999994</v>
       </c>
       <c r="I13" s="19">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"EQCH")</f>
-        <v>25722.762999999999</v>
+        <v>24662.312999999998</v>
       </c>
       <c r="J13" s="31">
-        <f t="shared" ref="J13:J15" si="15">I13/H13</f>
-        <v>0.91369174310198975</v>
+        <f t="shared" si="10"/>
+        <v>0.3820679464336455</v>
       </c>
       <c r="K13" s="39">
-        <f t="shared" si="0"/>
-        <v>51445.525999999998</v>
-      </c>
-      <c r="L13" s="53"/>
-      <c r="M13" s="50"/>
+        <f t="shared" si="11"/>
+        <v>44392.163399999998</v>
+      </c>
+      <c r="L13" s="51"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="63">
+        <f t="shared" ref="N13:N17" si="16">K13</f>
+        <v>44392.163399999998</v>
+      </c>
+      <c r="O13" s="27" t="str">
+        <f t="shared" ref="O13:O17" si="17">B13</f>
+        <v>CHF</v>
+      </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="36" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="44">
-        <v>0.18</v>
+        <v>125</v>
+      </c>
+      <c r="C14" s="55">
+        <v>0.1</v>
       </c>
       <c r="D14" s="19">
-        <f t="shared" si="11"/>
-        <v>36187.528930199995</v>
+        <f t="shared" si="12"/>
+        <v>19343.925748000005</v>
       </c>
       <c r="E14" s="25">
-        <f t="shared" ref="E14" si="16">$E$11*C14</f>
-        <v>15917.684642100001</v>
+        <f t="shared" ref="E14" si="18">$E$11*C14</f>
+        <v>8585.6678560000037</v>
       </c>
       <c r="F14" s="19">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"CBUK")</f>
-        <v>20772.2592</v>
+        <v>9923.6563999999998</v>
       </c>
       <c r="G14" s="31">
-        <f t="shared" ref="G14" si="17">F14/E14</f>
-        <v>1.304979943192262</v>
+        <f t="shared" ref="G14" si="19">F14/E14</f>
+        <v>1.1558397746617879</v>
       </c>
       <c r="H14" s="25">
-        <f t="shared" ref="H14" si="18">$H$11*C14</f>
-        <v>20269.844288099997</v>
+        <f t="shared" ref="H14" si="20">$H$11*C14</f>
+        <v>10758.257892000001</v>
       </c>
       <c r="I14" s="19">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"CBUK")</f>
-        <v>20772.2592</v>
+        <v>14885.4846</v>
       </c>
       <c r="J14" s="31">
-        <f t="shared" ref="J14" si="19">I14/H14</f>
-        <v>1.0247863232079666</v>
+        <f t="shared" si="10"/>
+        <v>1.3836333679144339</v>
       </c>
       <c r="K14" s="39">
-        <f t="shared" ref="K14" si="20">F14+I14</f>
-        <v>41544.518400000001</v>
-      </c>
-      <c r="L14" s="53"/>
-      <c r="M14" s="50"/>
+        <f t="shared" si="11"/>
+        <v>24809.141</v>
+      </c>
+      <c r="L14" s="51"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="63">
+        <f t="shared" si="16"/>
+        <v>24809.141</v>
+      </c>
+      <c r="O14" s="27" t="str">
+        <f t="shared" si="17"/>
+        <v>CHF</v>
+      </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="56" t="s">
-        <v>206</v>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="67" t="s">
+        <v>195</v>
       </c>
       <c r="B15" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="44">
-        <v>0.12</v>
+      <c r="C15" s="55">
+        <v>0.1</v>
       </c>
       <c r="D15" s="19">
-        <f t="shared" si="11"/>
-        <v>24125.019286799998</v>
+        <f t="shared" si="12"/>
+        <v>19343.925748000005</v>
       </c>
       <c r="E15" s="25">
-        <f t="shared" si="12"/>
-        <v>10611.789761400001</v>
+        <f t="shared" si="13"/>
+        <v>8585.6678560000037</v>
       </c>
       <c r="F15" s="19">
-        <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"2807")</f>
-        <v>0</v>
+        <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"9807")</f>
+        <v>7735</v>
       </c>
       <c r="G15" s="31">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>0.90092001341450412</v>
       </c>
       <c r="H15" s="25">
-        <f t="shared" si="13"/>
-        <v>13513.229525399998</v>
+        <f t="shared" si="15"/>
+        <v>10758.257892000001</v>
       </c>
       <c r="I15" s="19">
-        <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"2807")</f>
-        <v>0</v>
+        <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"9807")</f>
+        <v>8508.5</v>
       </c>
       <c r="J15" s="31">
-        <f t="shared" si="15"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>0.79088083641562879</v>
       </c>
       <c r="K15" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L15" s="53"/>
-      <c r="M15" s="50"/>
+        <f t="shared" si="11"/>
+        <v>16243.5</v>
+      </c>
+      <c r="L15" s="51"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="63">
+        <f t="shared" si="16"/>
+        <v>16243.5</v>
+      </c>
+      <c r="O15" s="27" t="str">
+        <f t="shared" si="17"/>
+        <v>USD</v>
+      </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="36" t="s">
         <v>8</v>
       </c>
       <c r="B16" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="55">
         <v>0.1</v>
       </c>
       <c r="D16" s="19">
-        <f t="shared" si="11"/>
-        <v>20104.182739</v>
+        <f t="shared" si="12"/>
+        <v>19343.925748000005</v>
       </c>
       <c r="E16" s="25">
         <f>$E$11*C16</f>
-        <v>8843.1581345000013</v>
+        <v>8585.6678560000037</v>
       </c>
       <c r="F16" s="19">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"INRA")</f>
-        <v>10733.03</v>
+        <v>10435.35</v>
       </c>
       <c r="G16" s="31">
         <f>F16/E16</f>
-        <v>1.213710061129293</v>
+        <v>1.2154383531978081</v>
       </c>
       <c r="H16" s="25">
         <f>$H$11*C16</f>
-        <v>11261.0246045</v>
+        <v>10758.257892000001</v>
       </c>
       <c r="I16" s="19">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"INRA")</f>
-        <v>10733.03</v>
+        <v>10435.35</v>
       </c>
       <c r="J16" s="31">
-        <f>I16/H16</f>
-        <v>0.95311309378642073</v>
+        <f t="shared" si="10"/>
+        <v>0.96998511327376524</v>
       </c>
       <c r="K16" s="39">
-        <f>F16+I16</f>
-        <v>21466.06</v>
-      </c>
-      <c r="L16" s="53"/>
-      <c r="M16" s="50"/>
+        <f t="shared" si="11"/>
+        <v>20870.7</v>
+      </c>
+      <c r="L16" s="51"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="63">
+        <f t="shared" si="16"/>
+        <v>20870.7</v>
+      </c>
+      <c r="O16" s="27" t="str">
+        <f t="shared" si="17"/>
+        <v>USD</v>
+      </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="36" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B17" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="55">
         <v>0.1</v>
       </c>
       <c r="D17" s="19">
-        <f t="shared" si="11"/>
-        <v>20104.182739</v>
+        <f t="shared" si="12"/>
+        <v>19343.925748000005</v>
       </c>
       <c r="E17" s="25">
         <f>$E$11*C17</f>
-        <v>8843.1581345000013</v>
+        <v>8585.6678560000037</v>
       </c>
       <c r="F17" s="19">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"GRDU")</f>
-        <v>4860</v>
+        <v>9113.6</v>
       </c>
       <c r="G17" s="31">
         <f>F17/E17</f>
-        <v>0.54957741635757684</v>
+        <v>1.0614899333231318</v>
       </c>
       <c r="H17" s="25">
         <f>$H$11*C17</f>
-        <v>11261.0246045</v>
+        <v>10758.257892000001</v>
       </c>
       <c r="I17" s="19">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"GRDU")</f>
-        <v>4860</v>
+        <v>9113.6</v>
       </c>
       <c r="J17" s="31">
-        <f>I17/H17</f>
-        <v>0.43157706964408044</v>
+        <f t="shared" si="10"/>
+        <v>0.84712600232208668</v>
       </c>
       <c r="K17" s="39">
-        <f>F17+I17</f>
-        <v>9720</v>
-      </c>
-      <c r="L17" s="53"/>
-      <c r="M17" s="50"/>
+        <f t="shared" si="11"/>
+        <v>18227.2</v>
+      </c>
+      <c r="L17" s="51"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="63">
+        <f t="shared" si="16"/>
+        <v>18227.2</v>
+      </c>
+      <c r="O17" s="27" t="str">
+        <f t="shared" si="17"/>
+        <v>USD</v>
+      </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="56"/>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="54"/>
       <c r="B18" s="42"/>
-      <c r="C18" s="44"/>
+      <c r="C18" s="55"/>
       <c r="D18" s="19"/>
       <c r="E18" s="25"/>
       <c r="F18" s="19"/>
@@ -7860,265 +8318,301 @@
       <c r="I18" s="19"/>
       <c r="J18" s="31"/>
       <c r="K18" s="39"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="50"/>
+      <c r="L18" s="51"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="27"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="35" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B19" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="43">
-        <v>0.2</v>
+      <c r="C19" s="56">
+        <v>0.15</v>
       </c>
       <c r="D19" s="18">
         <f>$G$42*C19</f>
-        <v>201041.82738999999</v>
+        <v>145079.44310999999</v>
       </c>
       <c r="E19" s="24">
         <f>$E$2*C19</f>
-        <v>88431.581345000013</v>
+        <v>64392.508920000007</v>
       </c>
       <c r="F19" s="18" cm="1">
         <f t="array" ref="F19">SUMPRODUCT(SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,IncomeStrategy!A:A))+SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"OPT")-SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"OPT",[1]PositionsHK!F:F,"SPY*")-SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"OPT",[1]PositionsHK!F:F,"QQQ*")+SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"FOP")-SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"FOP",[1]PositionsHK!F:F,"SPY*")-SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"FOP",[1]PositionsHK!F:F,"QQQ*")</f>
-        <v>43690.28</v>
+        <v>38310.83</v>
       </c>
       <c r="G19" s="30">
         <f>F19/E19</f>
-        <v>0.49405743214689535</v>
+        <v>0.59495787076097051</v>
       </c>
       <c r="H19" s="24">
         <f>$H$2*C19</f>
-        <v>112610.24604499999</v>
+        <v>80686.93419</v>
       </c>
       <c r="I19" s="18" cm="1">
         <f t="array" ref="I19">SUMPRODUCT(SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,IncomeStrategy!A:A))+SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"OPT")-SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"OPT",[1]PositionsAL!F:F,"SPY*")-SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"OPT",[1]PositionsAL!F:F,"QQQ*")+SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"FOP")-SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"FOP",[1]PositionsAL!F:F,"SPY*")-SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"FOP",[1]PositionsAL!F:F,"QQQ*")</f>
-        <v>61116.939999999995</v>
+        <v>56057.89</v>
       </c>
       <c r="J19" s="30">
-        <f t="shared" ref="J19:J23" si="21">I19/H19</f>
-        <v>0.54272983273277953</v>
+        <f>I19/H19</f>
+        <v>0.69475796252211031</v>
       </c>
       <c r="K19" s="38">
-        <f t="shared" si="0"/>
-        <v>104807.22</v>
-      </c>
-      <c r="L19" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="M19" s="50">
+        <f>F19+I19</f>
+        <v>94368.72</v>
+      </c>
+      <c r="L19" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="M19" s="48">
         <f t="shared" si="1"/>
-        <v>0.10426409405509932</v>
+        <v>9.7569357150532832E-2</v>
+      </c>
+      <c r="N19" s="63">
+        <f>K19</f>
+        <v>94368.72</v>
+      </c>
+      <c r="O19" s="27" t="str">
+        <f>B19</f>
+        <v>USD</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="B20" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="B20" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="56">
         <v>0.03</v>
       </c>
       <c r="D20" s="18">
         <f>$G$42*C20</f>
-        <v>30156.274108499998</v>
+        <v>29015.888621999999</v>
       </c>
       <c r="E20" s="24">
         <f>$E$2*C20</f>
-        <v>13264.73720175</v>
+        <v>12878.501784000002</v>
       </c>
       <c r="F20" s="18" cm="1">
         <f t="array" ref="F20">SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"STK")-SUMPRODUCT(SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"STK",[1]PositionsHK!F:F,GlobalETF!A:A))-SUMPRODUCT(SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"STK",[1]PositionsHK!F:F,GrowthEngine!A:A))-SUMPRODUCT(SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"STK",[1]PositionsHK!F:F,IncomeStrategy!A:A))-SUMPRODUCT(SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!D:D,"STK",[1]PositionsHK!F:F,Gold!A:A))</f>
-        <v>10576.000000000007</v>
+        <v>19545.766000000061</v>
       </c>
       <c r="G20" s="30">
-        <f t="shared" ref="G20:G21" si="22">F20/E20</f>
-        <v>0.79730188688583514</v>
+        <f t="shared" ref="G20:G21" si="21">F20/E20</f>
+        <v>1.5177049572865173</v>
       </c>
       <c r="H20" s="24">
         <f>$H$2*C20</f>
-        <v>16891.53690675</v>
+        <v>16137.386837999999</v>
       </c>
       <c r="I20" s="18" cm="1">
         <f t="array" ref="I20">SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"STK")-SUMPRODUCT(SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"STK",[1]PositionsAL!F:F,GlobalETF!A:A))-SUMPRODUCT(SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"STK",[1]PositionsAL!F:F,GrowthEngine!A:A))-SUMPRODUCT(SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"STK",[1]PositionsAL!F:F,IncomeStrategy!A:A))-SUMPRODUCT(SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!D:D,"STK",[1]PositionsAL!F:F,Gold!A:A))</f>
-        <v>4061.1700000000492</v>
+        <v>21674.226000000024</v>
       </c>
       <c r="J20" s="30">
         <f>I20/H20</f>
-        <v>0.24042631658799335</v>
+        <v>1.3431063044830769</v>
       </c>
       <c r="K20" s="38">
-        <f t="shared" si="0"/>
-        <v>14637.170000000056</v>
-      </c>
-      <c r="L20" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="M20" s="50">
+        <f>F20+I20</f>
+        <v>41219.992000000086</v>
+      </c>
+      <c r="L20" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="M20" s="48">
         <f t="shared" si="1"/>
-        <v>1.4561318099845448E-2</v>
+        <v>4.2618021323062499E-2</v>
+      </c>
+      <c r="N20" s="63">
+        <f t="shared" ref="N20:N22" si="22">K20</f>
+        <v>41219.992000000086</v>
+      </c>
+      <c r="O20" s="27" t="str">
+        <f t="shared" ref="O20:O22" si="23">B20</f>
+        <v>USD</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="B21" s="48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="56">
         <v>0.02</v>
       </c>
       <c r="D21" s="18">
         <f>$G$42*C21</f>
-        <v>20104.182739</v>
+        <v>19343.925748000001</v>
       </c>
       <c r="E21" s="24">
         <f>$E$2*C21</f>
-        <v>8843.1581344999995</v>
+        <v>8585.6678560000018</v>
       </c>
       <c r="F21" s="18">
         <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"SPY*",[1]PositionsHK!D:D,"OPT")+SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"SPY*",[1]PositionsHK!D:D,"FOP")+SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"QQQ*",[1]PositionsHK!D:D,"OPT")+SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"QQQ*",[1]PositionsHK!D:D,"FOP")</f>
-        <v>6896.24</v>
+        <v>8700.92</v>
       </c>
       <c r="G21" s="30">
-        <f t="shared" si="22"/>
-        <v>0.77983904563411044</v>
+        <f t="shared" si="21"/>
+        <v>1.013423783208601</v>
       </c>
       <c r="H21" s="24">
         <f>H2*C21</f>
-        <v>11261.024604499999</v>
+        <v>10758.257892</v>
       </c>
       <c r="I21" s="18">
         <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"SPY*",[1]PositionsAL!D:D,"OPT")+SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"SPY*",[1]PositionsAL!D:D,"FOP")+SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"QQQ*",[1]PositionsAL!D:D,"OPT")+SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"QQQ*",[1]PositionsAL!D:D,"FOP")</f>
-        <v>6896.24</v>
+        <v>8700.92</v>
       </c>
       <c r="J21" s="30">
         <f>I21/H21</f>
-        <v>0.61239898163833206</v>
+        <v>0.80876663186054809</v>
       </c>
       <c r="K21" s="38">
-        <f t="shared" si="0"/>
-        <v>13792.48</v>
-      </c>
-      <c r="L21" s="52" t="s">
-        <v>197</v>
-      </c>
-      <c r="M21" s="50">
+        <f>F21+I21</f>
+        <v>17401.84</v>
+      </c>
+      <c r="L21" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="M21" s="48">
         <f t="shared" si="1"/>
-        <v>1.3721005403760124E-2</v>
+        <v>1.799204590288422E-2</v>
+      </c>
+      <c r="N21" s="63">
+        <f t="shared" si="22"/>
+        <v>17401.84</v>
+      </c>
+      <c r="O21" s="27" t="str">
+        <f t="shared" si="23"/>
+        <v>USD</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B22" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="43">
-        <v>0.05</v>
+      <c r="C22" s="56">
+        <v>0.1</v>
       </c>
       <c r="D22" s="18">
         <f>$G$42*C22</f>
-        <v>50260.456847499998</v>
+        <v>96719.628740000015</v>
       </c>
       <c r="E22" s="24">
         <f>$E$2*C22</f>
-        <v>22107.895336250003</v>
-      </c>
-      <c r="F22" s="18">
-        <f>SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,"GSD")</f>
-        <v>23166.623025000001</v>
+        <v>42928.339280000015</v>
+      </c>
+      <c r="F22" s="18" cm="1">
+        <f t="array" ref="F22">SUMPRODUCT(SUMIFS([1]PositionsHK!V:V,[1]PositionsHK!F:F,Gold!A:A))</f>
+        <v>41199.404999999999</v>
       </c>
       <c r="G22" s="30">
-        <f t="shared" ref="G22:G23" si="23">F22/H22</f>
-        <v>0.82289574310111802</v>
+        <f>F22/E22</f>
+        <v>0.95972510679430101</v>
       </c>
       <c r="H22" s="24">
         <f>$H$2*C22</f>
-        <v>28152.561511249998</v>
-      </c>
-      <c r="I22" s="18">
-        <f>SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,"GSD")</f>
-        <v>23166.623025000001</v>
+        <v>53791.28946</v>
+      </c>
+      <c r="I22" s="18" cm="1">
+        <f t="array" ref="I22">SUMPRODUCT(SUMIFS([1]PositionsAL!V:V,[1]PositionsAL!F:F,Gold!A:A))</f>
+        <v>41199.404999999999</v>
       </c>
       <c r="J22" s="30">
-        <f t="shared" si="21"/>
-        <v>0.82289574310111802</v>
+        <f>I22/H22</f>
+        <v>0.76591220276726191</v>
       </c>
       <c r="K22" s="38">
-        <f t="shared" si="0"/>
-        <v>46333.246050000002</v>
-      </c>
-      <c r="L22" s="52" t="s">
-        <v>198</v>
-      </c>
-      <c r="M22" s="50">
+        <f>F22+I22</f>
+        <v>82398.81</v>
+      </c>
+      <c r="L22" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="M22" s="48">
         <f>K22/$G$42</f>
-        <v>4.6093140568324004E-2</v>
+        <v>8.5193472176679899E-2</v>
+      </c>
+      <c r="N22" s="63">
+        <f t="shared" si="22"/>
+        <v>82398.81</v>
+      </c>
+      <c r="O22" s="27" t="str">
+        <f t="shared" si="23"/>
+        <v>SGD</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B23" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="43">
+      <c r="C23" s="56">
         <v>0.05</v>
       </c>
       <c r="D23" s="18">
         <f>$G$42*C23</f>
-        <v>50260.456847499998</v>
+        <v>48359.814370000007</v>
       </c>
       <c r="E23" s="26">
         <f>$E$2*C23</f>
-        <v>22107.895336250003</v>
-      </c>
-      <c r="F23" s="45" t="str">
+        <v>21464.169640000007</v>
+      </c>
+      <c r="F23" s="58" t="str">
         <f>[1]Summary!$C$2</f>
-        <v>$114,463.22</v>
+        <v>$124,994.03</v>
       </c>
       <c r="G23" s="32">
-        <f t="shared" si="23"/>
-        <v>4.0658190180761897</v>
+        <f>F23/E23</f>
+        <v>5.8233806430165709</v>
       </c>
       <c r="H23" s="26">
         <f>$H$2*C23</f>
-        <v>28152.561511249998</v>
-      </c>
-      <c r="I23" s="45" t="str">
+        <v>26895.64473</v>
+      </c>
+      <c r="I23" s="58" t="str">
         <f>[1]Summary!$C$3</f>
-        <v>$113,399.16</v>
+        <v>$124,799.99</v>
       </c>
       <c r="J23" s="32">
-        <f t="shared" si="21"/>
-        <v>4.0280228125843811</v>
+        <f>I23/H23</f>
+        <v>4.6401561015860429</v>
       </c>
       <c r="K23" s="40">
-        <f t="shared" si="0"/>
-        <v>227862.38</v>
-      </c>
-      <c r="L23" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="M23" s="51">
+        <f>F23+I23</f>
+        <v>249794.02000000002</v>
+      </c>
+      <c r="L23" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="M23" s="49">
         <f>K23/$G$42</f>
-        <v>0.2266815646855129</v>
-      </c>
+        <v>0.25826610715338028</v>
+      </c>
+      <c r="N23" s="61"/>
+      <c r="O23" s="62"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="6">
         <f>C4+C11+C19+C20+C21+C22+C23</f>
-        <v>1.05</v>
+        <v>0.95000000000000018</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -8129,111 +8623,116 @@
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="F25" s="3"/>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
     </row>
     <row r="40" spans="7:14" x14ac:dyDescent="0.2">
       <c r="H40" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41" spans="7:14" x14ac:dyDescent="0.2">
       <c r="G41" s="12" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H41" s="11"/>
-      <c r="J41" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="K41" s="47" t="s">
-        <v>173</v>
-      </c>
-      <c r="L41" s="47"/>
+      <c r="J41" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="K41" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="L41" s="45"/>
     </row>
     <row r="42" spans="7:14" x14ac:dyDescent="0.2">
       <c r="G42" s="16">
         <f>E2+H2</f>
-        <v>1005209.13695</v>
+        <v>967196.28740000003</v>
       </c>
       <c r="H42" s="11"/>
       <c r="J42" t="s">
         <v>16</v>
       </c>
-      <c r="K42" s="46">
-        <v>365115.64</v>
-      </c>
-      <c r="L42" s="46"/>
+      <c r="K42" s="44">
+        <f>SUMIF(B4:B23, Query__2[[#This Row],[CurrencyPrimary]], N4:N23)</f>
+        <v>392933.95200000011</v>
+      </c>
+      <c r="L42" s="44"/>
     </row>
     <row r="43" spans="7:14" x14ac:dyDescent="0.2">
       <c r="G43" s="12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H43" s="17">
         <f>G44/G42</f>
-        <v>0.77331843531448707</v>
+        <v>0.74173389284661972</v>
       </c>
       <c r="J43" t="s">
-        <v>129</v>
-      </c>
-      <c r="K43" s="46">
-        <v>127769.98974999999</v>
-      </c>
-      <c r="L43" s="46"/>
+        <v>125</v>
+      </c>
+      <c r="K43" s="44">
+        <f>SUMIF(B4:B23, Query__2[[#This Row],[CurrencyPrimary]], N4:N23)</f>
+        <v>116320.94839999999</v>
+      </c>
+      <c r="L43" s="44"/>
     </row>
     <row r="44" spans="7:14" x14ac:dyDescent="0.2">
       <c r="G44" s="16">
         <f>G42-G46</f>
-        <v>777346.75694999995</v>
+        <v>717402.26740000001</v>
       </c>
       <c r="H44" s="11"/>
       <c r="J44" t="s">
         <v>12</v>
       </c>
-      <c r="K44" s="46">
-        <v>99402.54</v>
-      </c>
-      <c r="L44" s="46"/>
+      <c r="K44" s="44">
+        <f>SUMIF(B4:B23, Query__2[[#This Row],[CurrencyPrimary]], N4:N23)</f>
+        <v>51433.584999999999</v>
+      </c>
+      <c r="L44" s="44"/>
     </row>
     <row r="45" spans="7:14" x14ac:dyDescent="0.2">
       <c r="G45" s="12" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H45" s="17">
         <f>G46/G42</f>
-        <v>0.2266815646855129</v>
+        <v>0.25826610715338028</v>
       </c>
       <c r="J45" t="s">
         <v>14</v>
       </c>
-      <c r="K45" s="46">
-        <v>70588.302949999998</v>
-      </c>
-      <c r="L45" s="46"/>
+      <c r="K45" s="44">
+        <f>SUMIF(B4:B23, Query__2[[#This Row],[CurrencyPrimary]], N4:N23)</f>
+        <v>150209.20199999999</v>
+      </c>
+      <c r="L45" s="44"/>
     </row>
     <row r="46" spans="7:14" x14ac:dyDescent="0.2">
       <c r="G46" s="16">
         <f>F23+I23</f>
-        <v>227862.38</v>
+        <v>249794.02000000002</v>
       </c>
       <c r="H46" s="11"/>
       <c r="J46" t="s">
-        <v>174</v>
-      </c>
-      <c r="K46" s="46">
-        <v>18152.184000000001</v>
-      </c>
-      <c r="L46" s="46"/>
+        <v>10</v>
+      </c>
+      <c r="K46" s="44">
+        <f>SUMIF(B4:B23, Query__2[[#This Row],[CurrencyPrimary]], N4:N23)</f>
+        <v>22748.080000000002</v>
+      </c>
+      <c r="L46" s="44"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="11"/>
@@ -8241,7 +8740,7 @@
         <v>5</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E51" s="15"/>
       <c r="F51" s="15"/>
@@ -8253,11 +8752,11 @@
       </c>
       <c r="B52" s="13">
         <f>D4</f>
-        <v>502604.56847499998</v>
+        <v>386878.51496000006</v>
       </c>
       <c r="C52" s="14">
         <f>K4</f>
-        <v>385495.53649999999</v>
+        <v>373713.701</v>
       </c>
       <c r="E52" s="15"/>
       <c r="F52" s="15"/>
@@ -8269,11 +8768,11 @@
       </c>
       <c r="B53" s="13">
         <f>D11</f>
-        <v>201041.82738999999</v>
+        <v>193439.25748000003</v>
       </c>
       <c r="C53" s="14">
         <f>K11</f>
-        <v>212281.10440000001</v>
+        <v>108299.20439999999</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="15"/>
@@ -8285,11 +8784,11 @@
       </c>
       <c r="B54" s="13">
         <f>D19</f>
-        <v>201041.82738999999</v>
+        <v>145079.44310999999</v>
       </c>
       <c r="C54" s="14">
         <f>K19</f>
-        <v>104807.22</v>
+        <v>94368.72</v>
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="15"/>
@@ -8301,11 +8800,11 @@
       </c>
       <c r="B55" s="13">
         <f>D20</f>
-        <v>30156.274108499998</v>
+        <v>29015.888621999999</v>
       </c>
       <c r="C55" s="14">
         <f>K20</f>
-        <v>14637.170000000056</v>
+        <v>41219.992000000086</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="15"/>
@@ -8317,11 +8816,11 @@
       </c>
       <c r="B56" s="13">
         <f>D21</f>
-        <v>20104.182739</v>
+        <v>19343.925748000001</v>
       </c>
       <c r="C56" s="14">
         <f>K21</f>
-        <v>13792.48</v>
+        <v>17401.84</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="15"/>
@@ -8329,15 +8828,15 @@
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="str">
         <f>A22</f>
-        <v>The Vault (Gold)</v>
+        <v>The Vault (GSD, Gold)</v>
       </c>
       <c r="B57" s="13">
         <f>D22</f>
-        <v>50260.456847499998</v>
+        <v>96719.628740000015</v>
       </c>
       <c r="C57" s="14">
         <f>K22</f>
-        <v>46333.246050000002</v>
+        <v>82398.81</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
@@ -8349,18 +8848,19 @@
       </c>
       <c r="B58" s="13">
         <f>D23</f>
-        <v>50260.456847499998</v>
+        <v>48359.814370000007</v>
       </c>
       <c r="C58" s="14">
         <f>K23</f>
-        <v>227862.38</v>
+        <v>249794.02000000002</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G23">
     <cfRule type="expression" dxfId="19" priority="149">
@@ -8462,22 +8962,22 @@
         <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -8488,16 +8988,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D2" s="1">
         <v>3.8E-3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G2" s="1">
         <v>-6.3500000000000001E-2</v>
@@ -8511,19 +9011,19 @@
         <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -8534,19 +9034,19 @@
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -8557,65 +9057,65 @@
         <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -8625,7 +9125,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -8647,7 +9147,7 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>18</v>
@@ -8670,42 +9170,42 @@
         <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -8718,61 +9218,33 @@
         <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>191</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8801,402 +9273,402 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="E8" s="53" t="s">
         <v>55</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="55" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="55" t="s">
+      <c r="E9" s="53" t="s">
         <v>59</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="55" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="53" t="s">
         <v>62</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="55" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -9212,7 +9684,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -9230,30 +9702,47 @@
         <v>3</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="1" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>118</v>
+    </row>
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
